--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3147E751-9A33-432F-A6D0-39C490FB853F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64FE62C-13B9-45FB-BC2F-BF494F846859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 19-12-2025'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 29-01-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64FE62C-13B9-45FB-BC2F-BF494F846859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74821FC4-268F-485A-B027-0EDB4DEE1322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 29-01-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-02-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74821FC4-268F-485A-B027-0EDB4DEE1322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72FC248-43F9-48C1-A533-0CAD52F1F493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-02-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 20-02-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -638,9 +638,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -692,7 +692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -727,7 +727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -744,7 +744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -814,7 +814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -849,7 +849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -863,7 +863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -933,7 +933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -968,7 +968,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72FC248-43F9-48C1-A533-0CAD52F1F493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222B4895-2474-43C8-839B-AB5457593E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 20-02-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 04-03-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222B4895-2474-43C8-839B-AB5457593E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B9323B-6074-4DA1-9534-1B949E45864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 04-03-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-03-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>Standard</t>
   </si>
@@ -70,22 +70,26 @@
     <t>Godkendt</t>
   </si>
   <si>
+    <t>Binær dokumenttransport</t>
+  </si>
+  <si>
+    <t>BIN01 (B0131X)</t>
+  </si>
+  <si>
+    <t>Ikke Godkendt</t>
+  </si>
+  <si>
+    <t>CareCommunication</t>
+  </si>
+  <si>
+    <t>CareCommunication (4.0)</t>
+  </si>
+  <si>
     <t>Tester</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
-  </si>
-  <si>
-    <t>BIN01 (B0131X)</t>
-  </si>
-  <si>
-    <t>Ikke Godkendt</t>
-  </si>
-  <si>
-    <t>CareCommunication</t>
-  </si>
-  <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0_x000D_
+5.0)</t>
   </si>
   <si>
     <t>Negativ VANS kvittering</t>
@@ -637,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -689,16 +693,16 @@
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
@@ -706,7 +710,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -729,62 +733,41 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -816,10 +799,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -851,60 +834,60 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
       <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
@@ -912,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -935,11 +918,11 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -947,7 +930,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
@@ -970,11 +953,11 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
@@ -982,7 +965,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
@@ -1005,11 +988,11 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
@@ -1017,7 +1000,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -1040,11 +1023,11 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
@@ -1052,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -1061,6 +1044,9 @@
         <v>14</v>
       </c>
       <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" t="s">
         <v>14</v>
       </c>
       <c r="J14" t="s">
@@ -1072,7 +1058,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
@@ -1084,7 +1070,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -1093,9 +1079,6 @@
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" t="s">
         <v>14</v>
       </c>
       <c r="J15" t="s">
@@ -1107,11 +1090,11 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
@@ -1119,7 +1102,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
@@ -1142,11 +1125,11 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
@@ -1154,7 +1137,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
@@ -1177,11 +1160,11 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -1189,7 +1172,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -1212,11 +1195,11 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
@@ -1224,7 +1207,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
@@ -1247,11 +1230,11 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
@@ -1259,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
@@ -1268,6 +1251,9 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" t="s">
         <v>14</v>
       </c>
       <c r="J20" t="s">
@@ -1279,11 +1265,11 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
@@ -1291,7 +1277,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
@@ -1300,9 +1286,6 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" t="s">
         <v>14</v>
       </c>
       <c r="J21" t="s">
@@ -1314,11 +1297,11 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -1326,7 +1309,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
@@ -1349,11 +1332,11 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
@@ -1361,7 +1344,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -1384,13 +1367,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
       <c r="C24" t="s">
         <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" t="s">
+        <v>14</v>
       </c>
       <c r="K24" t="s">
         <v>14</v>
@@ -1398,31 +1402,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
       <c r="C25" t="s">
         <v>13</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" t="s">
-        <v>14</v>
       </c>
       <c r="K25" t="s">
         <v>14</v>
@@ -1430,13 +1416,31 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
       <c r="C26" t="s">
         <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" t="s">
+        <v>14</v>
       </c>
       <c r="K26" t="s">
         <v>14</v>
@@ -1444,10 +1448,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>64</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -1458,34 +1462,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
       <c r="C28" t="s">
         <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>14</v>
       </c>
       <c r="K28" t="s">
         <v>14</v>
@@ -1493,11 +1476,11 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
@@ -1505,16 +1488,19 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>20</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
@@ -1525,7 +1511,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
         <v>70</v>
@@ -1537,7 +1523,7 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -1547,9 +1533,6 @@
       </c>
       <c r="H30" t="s">
         <v>14</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
@@ -1560,60 +1543,60 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
         <v>73</v>
       </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="D32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
       <c r="I32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
@@ -1621,7 +1604,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -1630,6 +1613,9 @@
         <v>14</v>
       </c>
       <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" t="s">
         <v>14</v>
       </c>
       <c r="J33" t="s">
@@ -1641,11 +1627,11 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
         <v>77</v>
       </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
@@ -1653,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -1662,9 +1648,6 @@
         <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" t="s">
         <v>14</v>
       </c>
       <c r="J34" t="s">
@@ -1676,11 +1659,11 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
         <v>79</v>
       </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
@@ -1688,7 +1671,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -1711,60 +1694,60 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
         <v>81</v>
       </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
       <c r="I36" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
         <v>83</v>
       </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
-        <v>14</v>
-      </c>
       <c r="I37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>85</v>
       </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
@@ -1772,7 +1755,7 @@
         <v>14</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -1795,21 +1778,30 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
+      <c r="G39" t="s">
+        <v>14</v>
+      </c>
       <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
         <v>14</v>
       </c>
       <c r="J39" t="s">
@@ -1821,36 +1813,62 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
         <v>89</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>90</v>
       </c>
-      <c r="C40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B9323B-6074-4DA1-9534-1B949E45864C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3A98CC-FB9E-48BD-B98B-3A72975606B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3A98CC-FB9E-48BD-B98B-3A72975606B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C267FA-73FC-4074-8B7D-FEF8525F3C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C267FA-73FC-4074-8B7D-FEF8525F3C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844794A4-A4A8-43D9-AD12-64B3861B9BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-03-2026'!$A$1:$K$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-03-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844794A4-A4A8-43D9-AD12-64B3861B9BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFB3D1E-3A1B-4847-8297-A3894287F38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFB3D1E-3A1B-4847-8297-A3894287F38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC26AFAB-08E9-4A8B-A76D-461D1E34F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-03-2026'!$A$1:$K$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC26AFAB-08E9-4A8B-A76D-461D1E34F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF44D1BE-7652-4DAD-9DC2-3B55E0E680BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="90">
   <si>
     <t>Standard</t>
   </si>
@@ -240,12 +240,6 @@
   </si>
   <si>
     <t>REF06 (H0631R)</t>
-  </si>
-  <si>
-    <t>Psykologhenvisning</t>
-  </si>
-  <si>
-    <t>REF10 (H1031R)</t>
   </si>
   <si>
     <t>Laboratoriesvar</t>
@@ -641,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1586,8 +1580,29 @@
       <c r="C32" t="s">
         <v>13</v>
       </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -1615,9 +1630,6 @@
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" t="s">
-        <v>14</v>
-      </c>
       <c r="J33" t="s">
         <v>14</v>
       </c>
@@ -1650,6 +1662,9 @@
       <c r="H34" t="s">
         <v>14</v>
       </c>
+      <c r="I34" t="s">
+        <v>14</v>
+      </c>
       <c r="J34" t="s">
         <v>14</v>
       </c>
@@ -1702,28 +1717,7 @@
       <c r="C36" t="s">
         <v>13</v>
       </c>
-      <c r="D36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>14</v>
-      </c>
       <c r="I36" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" t="s">
-        <v>14</v>
-      </c>
-      <c r="K36" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1737,7 +1731,28 @@
       <c r="C37" t="s">
         <v>13</v>
       </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
       <c r="I37" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1789,19 +1804,10 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39" t="s">
-        <v>17</v>
-      </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
       <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" t="s">
         <v>14</v>
       </c>
       <c r="J39" t="s">
@@ -1824,51 +1830,25 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
       <c r="H40" t="s">
         <v>14</v>
       </c>
+      <c r="I40" t="s">
+        <v>14</v>
+      </c>
       <c r="J40" t="s">
         <v>14</v>
       </c>
       <c r="K40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF44D1BE-7652-4DAD-9DC2-3B55E0E680BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88618886-C669-41AC-8A35-FEF046F3FFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 20-03-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88618886-C669-41AC-8A35-FEF046F3FFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C52C606-16AD-44A5-9510-F2A531EA47B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 20-03-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 25-03-2026'!$A$1:$K$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C52C606-16AD-44A5-9510-F2A531EA47B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1C8527-2807-4608-8FD5-47E73669F8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 25-03-2026'!$A$1:$K$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 08-04-2026'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="93">
   <si>
     <t>Standard</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>WinPLC _LPS_ (EG)</t>
+  </si>
+  <si>
+    <t>Xmedicus _LPS_ (Xmedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -114,6 +117,13 @@
   </si>
   <si>
     <t>DDB (1.1)</t>
+  </si>
+  <si>
+    <t>Den Gode Blanketservice</t>
+  </si>
+  <si>
+    <t>DGB (0.91_x000D_
+0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
@@ -635,10 +645,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -672,1184 +682,1231 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" t="s">
         <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="L29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
         <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>14</v>
-      </c>
-      <c r="K38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="L40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1C8527-2807-4608-8FD5-47E73669F8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67C591C-6668-4447-8DEF-C389A99A309D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 08-04-2026'!$A$1:$L$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 10-04-2026'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67C591C-6668-4447-8DEF-C389A99A309D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55B68A0-9821-4CCD-8F07-A52FD81E6E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
@@ -122,8 +122,7 @@
     <t>Den Gode Blanketservice</t>
   </si>
   <si>
-    <t>DGB (0.91_x000D_
-0.91)</t>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Udskrivningsepikrise</t>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55B68A0-9821-4CCD-8F07-A52FD81E6E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75BE247-064F-4592-96BD-376E03F17A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 10-04-2026'!$A$1:$L$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 14-04-2026'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75BE247-064F-4592-96BD-376E03F17A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2203FED-A92F-4310-A700-CB4DC72568DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 14-04-2026'!$A$1:$L$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 24-04-2026'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2203FED-A92F-4310-A700-CB4DC72568DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FC36C3-12E4-4EA1-B119-2320C9F4F56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FC36C3-12E4-4EA1-B119-2320C9F4F56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EB6C20-E171-4AA6-BDCE-CA0B37FD0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 24-04-2026'!$A$1:$L$41</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 27-04-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>Standard</t>
   </si>
@@ -85,14 +85,10 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Tester</t>
-  </si>
-  <si>
-    <t>CareCommunication (5.0_x000D_
-5.0)</t>
   </si>
   <si>
     <t>Negativ VANS kvittering</t>
@@ -644,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -751,32 +747,56 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
       <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -811,10 +831,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -849,54 +869,30 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
       <c r="I8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
       <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
@@ -904,24 +900,45 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="K10" t="s">
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -953,10 +970,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -988,10 +1005,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -1000,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1015,6 +1032,9 @@
         <v>15</v>
       </c>
       <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
         <v>15</v>
       </c>
       <c r="L13" t="s">
@@ -1023,10 +1043,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -1035,7 +1055,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -1050,9 +1070,6 @@
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" t="s">
         <v>15</v>
       </c>
       <c r="L14" t="s">
@@ -1061,10 +1078,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -1073,7 +1090,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -1082,9 +1099,6 @@
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
@@ -1096,7 +1110,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>44</v>
@@ -1108,7 +1122,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1119,8 +1133,14 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
       <c r="J16" t="s">
         <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1128,10 +1148,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -1140,7 +1160,7 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
@@ -1158,7 +1178,7 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L17" t="s">
         <v>15</v>
@@ -1166,10 +1186,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -1178,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1193,9 +1213,6 @@
         <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
         <v>15</v>
       </c>
       <c r="L18" t="s">
@@ -1204,10 +1221,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -1239,10 +1256,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -1251,7 +1268,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
@@ -1266,6 +1283,9 @@
         <v>15</v>
       </c>
       <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
         <v>15</v>
       </c>
       <c r="L20" t="s">
@@ -1274,10 +1294,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -1286,7 +1306,7 @@
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
@@ -1297,13 +1317,7 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
       <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
         <v>15</v>
       </c>
       <c r="L21" t="s">
@@ -1312,10 +1326,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -1335,7 +1349,13 @@
       <c r="H22" t="s">
         <v>15</v>
       </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
       <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s">
         <v>15</v>
       </c>
       <c r="L22" t="s">
@@ -1344,10 +1364,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -1371,9 +1391,6 @@
         <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" t="s">
         <v>15</v>
       </c>
       <c r="L23" t="s">
@@ -1382,10 +1399,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -1417,34 +1434,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -1452,13 +1448,31 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
       </c>
       <c r="L26" t="s">
         <v>15</v>
@@ -1466,31 +1480,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1498,10 +1494,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -1512,13 +1508,34 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1526,10 +1543,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -1538,19 +1555,16 @@
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>21</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1561,7 +1575,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
         <v>73</v>
@@ -1573,7 +1587,7 @@
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
         <v>15</v>
@@ -1583,6 +1597,9 @@
       </c>
       <c r="H31" t="s">
         <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -1593,10 +1610,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -1617,7 +1634,7 @@
         <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -1628,10 +1645,10 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -1649,9 +1666,6 @@
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" t="s">
         <v>15</v>
       </c>
       <c r="J33" t="s">
@@ -1663,10 +1677,10 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -1684,6 +1698,9 @@
         <v>15</v>
       </c>
       <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s">
         <v>15</v>
       </c>
       <c r="J34" t="s">
@@ -1695,10 +1712,10 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -1730,59 +1747,59 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
       <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
       <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -1814,10 +1831,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -1825,19 +1842,10 @@
       <c r="D39" t="s">
         <v>15</v>
       </c>
-      <c r="E39" t="s">
-        <v>18</v>
-      </c>
       <c r="F39" t="s">
         <v>15</v>
       </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
       <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
         <v>15</v>
       </c>
       <c r="J39" t="s">
@@ -1849,10 +1857,10 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -1860,51 +1868,25 @@
       <c r="D40" t="s">
         <v>15</v>
       </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
       <c r="F40" t="s">
         <v>15</v>
       </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
       <c r="H40" t="s">
         <v>15</v>
       </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
       <c r="J40" t="s">
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L41" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EB6C20-E171-4AA6-BDCE-CA0B37FD0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BAD2F7-B943-492C-8E8A-95B94306D89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 27-04-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-05-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BAD2F7-B943-492C-8E8A-95B94306D89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062D5B8F-D810-4F74-B997-37F90E338EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-05-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 01-06-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062D5B8F-D810-4F74-B997-37F90E338EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDBB6F6-D1C2-4CEC-AB46-459D319896C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 01-06-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-06-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDBB6F6-D1C2-4CEC-AB46-459D319896C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62A3CD7-1CF0-455A-9872-EEFC4D973C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
   <si>
     <t>Standard</t>
   </si>
@@ -1317,6 +1317,9 @@
       <c r="H21" t="s">
         <v>15</v>
       </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62A3CD7-1CF0-455A-9872-EEFC4D973C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960BCAEA-7E3E-4FCF-AD9F-C973607C03BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-06-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 05-06-2026'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64FE62C-13B9-45FB-BC2F-BF494F846859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9616E24-5A12-43C9-B9F7-8C64A2D0BB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC4B99F-51C8-44DE-87DD-AC8D1E23BC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA39731-E0DA-4C45-93C4-6E6ED76044AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA39731-E0DA-4C45-93C4-6E6ED76044AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158D5F10-6C1C-41DC-8FDD-20FB64D0A1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-06-2026'!$A$1:$L$40</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>XDS Metadata (0.96)</t>
+  </si>
+  <si>
+    <t>CervixcytologyReport</t>
+  </si>
+  <si>
+    <t>XRPT03 (XR0331P)</t>
+  </si>
+  <si>
+    <t>HistopathologyReport</t>
+  </si>
+  <si>
+    <t>XRPT04 (XR0432P)</t>
   </si>
   <si>
     <t>MicrobiologyWebReport</t>
@@ -640,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1709,6 +1721,9 @@
       <c r="J34" t="s">
         <v>15</v>
       </c>
+      <c r="K34" t="s">
+        <v>15</v>
+      </c>
       <c r="L34" t="s">
         <v>15</v>
       </c>
@@ -1744,6 +1759,9 @@
       <c r="J35" t="s">
         <v>15</v>
       </c>
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
       <c r="L35" t="s">
         <v>15</v>
       </c>
@@ -1868,28 +1886,59 @@
       <c r="C40" t="s">
         <v>14</v>
       </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="K40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158D5F10-6C1C-41DC-8FDD-20FB64D0A1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4034B33-1EE6-4965-8A15-EC42D57871B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 15-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -710,7 +710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -748,7 +748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -803,7 +803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -879,7 +879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -896,7 +896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -910,7 +910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4034B33-1EE6-4965-8A15-EC42D57871B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9D3577-7277-44EC-AD28-FD74ADE33409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 15-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -1654,6 +1654,9 @@
       <c r="J32" t="s">
         <v>15</v>
       </c>
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
       <c r="L32" t="s">
         <v>15</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9D3577-7277-44EC-AD28-FD74ADE33409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B310150E-A9ED-4E59-8974-E178ED8BCD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -710,7 +710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -748,7 +748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -765,7 +765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -803,7 +803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -879,7 +879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -896,7 +896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -910,7 +910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -980,7 +980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B310150E-A9ED-4E59-8974-E178ED8BCD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70FE6A84-D118-48BB-9C2A-F58D3A1C1383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9D3577-7277-44EC-AD28-FD74ADE33409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37530AE-5690-4E5B-80B5-493E339D2B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37530AE-5690-4E5B-80B5-493E339D2B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50358932-8560-4E1A-867D-E3EC311E7161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 25-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50358932-8560-4E1A-867D-E3EC311E7161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D9F47-4F61-4392-8A71-E5AAA272B2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 25-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 30-06-2026'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D9F47-4F61-4392-8A71-E5AAA272B2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AE4E1D-94B6-4E66-A501-EDC2C90ED9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AE4E1D-94B6-4E66-A501-EDC2C90ED9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB2B9EE-AE09-4244-BCC1-121B820CA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 30-06-2026'!$A$1:$L$42</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="97">
   <si>
     <t>Standard</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Udskrivningsepikrise</t>
+  </si>
+  <si>
+    <t>DIS01 (D0133L)</t>
   </si>
   <si>
     <t>DIS01 (D0134L)</t>
@@ -652,10 +655,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -710,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -748,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -765,7 +768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -803,7 +806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -841,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -879,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -896,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -910,7 +913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -920,209 +923,200 @@
       <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>44</v>
@@ -1134,7 +1128,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1145,452 +1139,458 @@
       <c r="H16" t="s">
         <v>15</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
-      </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
         <v>21</v>
       </c>
-      <c r="L16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="L17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>46</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>47</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>49</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>50</v>
       </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>51</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>52</v>
       </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>53</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>54</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
         <v>21</v>
       </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>56</v>
       </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>57</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>58</v>
       </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" t="s">
-        <v>15</v>
-      </c>
-      <c r="L23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>59</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>60</v>
       </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>61</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>63</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>64</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>65</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>66</v>
       </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>67</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>68</v>
       </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>69</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
         <v>21</v>
       </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>71</v>
       </c>
       <c r="B31" t="s">
         <v>73</v>
@@ -1602,7 +1602,7 @@
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>15</v>
@@ -1613,335 +1613,367 @@
       <c r="H31" t="s">
         <v>15</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
         <v>21</v>
       </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>75</v>
       </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>76</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>77</v>
       </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
-      </c>
-      <c r="L33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>82</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>83</v>
       </c>
-      <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>84</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>87</v>
       </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>89</v>
       </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>90</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>91</v>
       </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>93</v>
       </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42" t="s">
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" t="s">
         <v>15</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB2B9EE-AE09-4244-BCC1-121B820CA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D9B5EA-6543-43F7-8407-232A8F98BDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-07-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB2B9EE-AE09-4244-BCC1-121B820CA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70BF548-3B1C-4DF0-B50B-223CC5568287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -768,7 +768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -844,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -899,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -913,7 +913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -927,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D9B5EA-6543-43F7-8407-232A8F98BDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A413A9-5EC5-43FB-BF8B-95FAA2F9AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-07-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -768,7 +768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -844,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -899,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -913,7 +913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -927,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A413A9-5EC5-43FB-BF8B-95FAA2F9AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0886EA71-7DB2-4DE9-BB78-61564686FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-07-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0886EA71-7DB2-4DE9-BB78-61564686FB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E074DD05-E9FE-4822-9A26-07C15A4D135E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-07-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 19-08-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E074DD05-E9FE-4822-9A26-07C15A4D135E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956690B6-5DD5-4816-B2FA-5285C5ACD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 19-08-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 21-08-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -768,7 +768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -844,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -899,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -913,7 +913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -927,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>95</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956690B6-5DD5-4816-B2FA-5285C5ACD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1706F02E-2FF8-48BD-BA2E-C50C62C304B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 21-08-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 27-08-2026'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -768,7 +768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -806,7 +806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -844,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -899,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -913,7 +913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -927,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1706F02E-2FF8-48BD-BA2E-C50C62C304B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7DF1A1-E510-456F-A262-2C3CB2225680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 27-08-2026'!$A$1:$L$43</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="108">
   <si>
     <t>Standard</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Clinea _LPS_ (EG)</t>
   </si>
   <si>
+    <t>DokuDok (DokuDok)</t>
+  </si>
+  <si>
     <t>Journal _LPS_ (DMDC)</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
     <t>Godkendt</t>
   </si>
   <si>
+    <t>Tester</t>
+  </si>
+  <si>
     <t>Binær dokumenttransport</t>
   </si>
   <si>
@@ -88,9 +94,6 @@
     <t>CareCommunication (5.0)</t>
   </si>
   <si>
-    <t>Tester</t>
-  </si>
-  <si>
     <t>Negativ VANS kvittering</t>
   </si>
   <si>
@@ -277,13 +280,43 @@
     <t>Den gode VANSEnvelope</t>
   </si>
   <si>
+    <t>VANSEnvelope (1.0)</t>
+  </si>
+  <si>
     <t>VANSEnvelope (1.0.4)</t>
   </si>
   <si>
+    <t>BinaryLetter</t>
+  </si>
+  <si>
+    <t>XBIN01 (XB0131X)</t>
+  </si>
+  <si>
+    <t>NegativeVansReceipt</t>
+  </si>
+  <si>
+    <t>XCTL01 (XC0130Q)</t>
+  </si>
+  <si>
+    <t>NegativeReceipt</t>
+  </si>
+  <si>
+    <t>XCTL02 (XC0230Q)</t>
+  </si>
+  <si>
+    <t>PositiveReceipt</t>
+  </si>
+  <si>
+    <t>XCTL03 (XC0330Q)</t>
+  </si>
+  <si>
     <t>MunicipalityLetter</t>
   </si>
   <si>
     <t>XDIS15 (XD1530L)</t>
+  </si>
+  <si>
+    <t>XDIS15 (XD1534L)</t>
   </si>
   <si>
     <t>EmergencyMunicipalityLetter</t>
@@ -655,10 +688,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -695,1162 +728,1213 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K24" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="K25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="M26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="L28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="M28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K30" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>72</v>
-      </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="K32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="M36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>85</v>
       </c>
       <c r="B38" t="s">
         <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
         <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1858,34 +1942,13 @@
         <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1893,25 +1956,13 @@
         <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1919,13 +1970,13 @@
         <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1933,13 +1984,13 @@
         <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="K42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -1947,34 +1998,178 @@
         <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="s">
-        <v>15</v>
-      </c>
-      <c r="L43" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="M43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46" t="s">
+        <v>16</v>
+      </c>
+      <c r="M46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="L47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" t="s">
+        <v>16</v>
+      </c>
+      <c r="L49" t="s">
+        <v>16</v>
+      </c>
+      <c r="M49" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7DF1A1-E510-456F-A262-2C3CB2225680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EA36C6-625A-4D81-870E-4A115B54044B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 02-09-2026'!$A$1:$M$49</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-09-2026'!$A$1:$M$50</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="110">
   <si>
     <t>Standard</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>REF06 (H0631R)</t>
+  </si>
+  <si>
+    <t>Psykologhenvisning</t>
+  </si>
+  <si>
+    <t>REF10 (H1031R)</t>
   </si>
   <si>
     <t>Laboratoriesvar</t>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1761,35 +1767,8 @@
       <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s">
-        <v>16</v>
-      </c>
       <c r="J33" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" t="s">
-        <v>16</v>
-      </c>
-      <c r="L33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -1805,6 +1784,9 @@
       <c r="D34" t="s">
         <v>16</v>
       </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
       <c r="F34" t="s">
         <v>20</v>
       </c>
@@ -1817,7 +1799,13 @@
       <c r="I34" t="s">
         <v>16</v>
       </c>
+      <c r="J34" t="s">
+        <v>16</v>
+      </c>
       <c r="K34" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" t="s">
         <v>16</v>
       </c>
       <c r="M34" t="s">
@@ -1837,9 +1825,6 @@
       <c r="D35" t="s">
         <v>16</v>
       </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
       <c r="F35" t="s">
         <v>20</v>
       </c>
@@ -1852,13 +1837,7 @@
       <c r="I35" t="s">
         <v>16</v>
       </c>
-      <c r="J35" t="s">
-        <v>16</v>
-      </c>
       <c r="K35" t="s">
-        <v>16</v>
-      </c>
-      <c r="L35" t="s">
         <v>16</v>
       </c>
       <c r="M35" t="s">
@@ -1916,27 +1895,54 @@
       <c r="C37" t="s">
         <v>15</v>
       </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
       <c r="E37" t="s">
         <v>17</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="J38" t="s">
-        <v>16</v>
+      <c r="E38" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
         <v>88</v>
@@ -1944,8 +1950,8 @@
       <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="E39" t="s">
-        <v>17</v>
+      <c r="J39" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -2000,48 +2006,48 @@
       <c r="C43" t="s">
         <v>15</v>
       </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" t="s">
-        <v>16</v>
+      <c r="E43" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
       </c>
-      <c r="E44" t="s">
-        <v>17</v>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
         <v>99</v>
@@ -2049,32 +2055,8 @@
       <c r="C45" t="s">
         <v>15</v>
       </c>
-      <c r="D45" t="s">
-        <v>16</v>
-      </c>
       <c r="E45" t="s">
         <v>17</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -2090,10 +2072,22 @@
       <c r="D46" t="s">
         <v>16</v>
       </c>
+      <c r="E46" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
       <c r="G46" t="s">
         <v>16</v>
       </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
       <c r="I46" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" t="s">
         <v>16</v>
       </c>
       <c r="K46" t="s">
@@ -2113,7 +2107,19 @@
       <c r="C47" t="s">
         <v>15</v>
       </c>
-      <c r="L47" t="s">
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" t="s">
+        <v>16</v>
+      </c>
+      <c r="M47" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2141,34 +2147,48 @@
       <c r="C49" t="s">
         <v>15</v>
       </c>
-      <c r="D49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" t="s">
-        <v>16</v>
-      </c>
-      <c r="H49" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" t="s">
-        <v>16</v>
-      </c>
       <c r="L49" t="s">
         <v>16</v>
       </c>
-      <c r="M49" t="s">
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" t="s">
+        <v>16</v>
+      </c>
+      <c r="M50" t="s">
         <v>16</v>
       </c>
     </row>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EA36C6-625A-4D81-870E-4A115B54044B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD3CE8E-3245-4CB0-942E-0093899A48AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD3CE8E-3245-4CB0-942E-0093899A48AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B2AF55-6DE5-462E-9B34-147D5F234260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 06-09-2026'!$A$1:$M$50</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 07-09-2026'!$A$1:$M$50</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B2AF55-6DE5-462E-9B34-147D5F234260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8A3534-FEC2-4E51-8D7E-773D83128737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 07-09-2026'!$A$1:$M$50</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$M$50</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="110">
   <si>
     <t>Standard</t>
   </si>
@@ -1680,9 +1680,6 @@
       <c r="I30" t="s">
         <v>16</v>
       </c>
-      <c r="J30" t="s">
-        <v>17</v>
-      </c>
       <c r="K30" t="s">
         <v>16</v>
       </c>
@@ -1746,9 +1743,6 @@
       </c>
       <c r="I32" t="s">
         <v>16</v>
-      </c>
-      <c r="J32" t="s">
-        <v>17</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>

--- a/html/Lægesystemer - modtage_excel.XLSX
+++ b/html/Lægesystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8A3534-FEC2-4E51-8D7E-773D83128737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BC32A4-5EA9-468E-A8F8-EF482A9636DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$M$50</definedName>
+    <definedName name="Lægesystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="108">
   <si>
     <t>Standard</t>
   </si>
@@ -251,12 +251,6 @@
   </si>
   <si>
     <t>REF06 (H0631R)</t>
-  </si>
-  <si>
-    <t>Psykologhenvisning</t>
-  </si>
-  <si>
-    <t>REF10 (H1031R)</t>
   </si>
   <si>
     <t>Laboratoriesvar</t>
@@ -694,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1761,8 +1755,35 @@
       <c r="C33" t="s">
         <v>15</v>
       </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
+      </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -1778,9 +1799,6 @@
       <c r="D34" t="s">
         <v>16</v>
       </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
       <c r="F34" t="s">
         <v>20</v>
       </c>
@@ -1793,13 +1811,7 @@
       <c r="I34" t="s">
         <v>16</v>
       </c>
-      <c r="J34" t="s">
-        <v>16</v>
-      </c>
       <c r="K34" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" t="s">
         <v>16</v>
       </c>
       <c r="M34" t="s">
@@ -1819,6 +1831,9 @@
       <c r="D35" t="s">
         <v>16</v>
       </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
       <c r="F35" t="s">
         <v>20</v>
       </c>
@@ -1831,7 +1846,13 @@
       <c r="I35" t="s">
         <v>16</v>
       </c>
+      <c r="J35" t="s">
+        <v>16</v>
+      </c>
       <c r="K35" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" t="s">
         <v>16</v>
       </c>
       <c r="M35" t="s">
@@ -1889,54 +1910,27 @@
       <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
       <c r="E37" t="s">
         <v>17</v>
-      </c>
-      <c r="F37" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K37" t="s">
-        <v>16</v>
-      </c>
-      <c r="L37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="E38" t="s">
-        <v>17</v>
+      <c r="J38" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>88</v>
@@ -1944,8 +1938,8 @@
       <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="J39" t="s">
-        <v>16</v>
+      <c r="E39" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -2000,48 +1994,48 @@
       <c r="C43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="s">
-        <v>17</v>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
       <c r="C44" t="s">
         <v>15</v>
       </c>
-      <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" t="s">
-        <v>16</v>
-      </c>
-      <c r="K44" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" t="s">
-        <v>16</v>
+      <c r="E44" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B45" t="s">
         <v>99</v>
@@ -2049,8 +2043,32 @@
       <c r="C45" t="s">
         <v>15</v>
       </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
       <c r="E45" t="s">
         <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -2066,22 +2084,10 @@
       <c r="D46" t="s">
         <v>16</v>
       </c>
-      <c r="E46" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
       <c r="G46" t="s">
         <v>16</v>
       </c>
-      <c r="H46" t="s">
-        <v>16</v>
-      </c>
       <c r="I46" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" t="s">
         <v>16</v>
       </c>
       <c r="K46" t="s">
@@ -2101,19 +2107,7 @@
       <c r="C47" t="s">
         <v>15</v>
       </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" t="s">
+      <c r="L47" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2141,48 +2135,34 @@
       <c r="C49" t="s">
         <v>15</v>
       </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" t="s">
+        <v>16</v>
+      </c>
       <c r="L49" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" t="s">
-        <v>16</v>
-      </c>
-      <c r="E50" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" t="s">
-        <v>16</v>
-      </c>
-      <c r="K50" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" t="s">
-        <v>16</v>
-      </c>
-      <c r="M50" t="s">
+      <c r="M49" t="s">
         <v>16</v>
       </c>
     </row>
